--- a/apps/web/public/templates/ledger-template.xlsx
+++ b/apps/web/public/templates/ledger-template.xlsx
@@ -398,33 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y1"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="14.83203125" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" customWidth="1"/>
-    <col min="23" max="23" width="14.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,7 +416,7 @@
         <v>订单号</v>
       </c>
       <c r="F1" t="str">
-        <v>跟踪号</v>
+        <v>SKU</v>
       </c>
       <c r="G1" t="str">
         <v>售价</v>

--- a/apps/web/public/templates/ledger-template.xlsx
+++ b/apps/web/public/templates/ledger-template.xlsx
@@ -470,7 +470,7 @@
         <v>30%净利</v>
       </c>
       <c r="X1" t="str">
-        <v>赔偿</v>
+        <v>尾程</v>
       </c>
       <c r="Y1" t="str">
         <v>备注</v>
